--- a/worklog/v2.2.3/s10/pjm/v3/test/ods_material_info_v2.xlsx
+++ b/worklog/v2.2.3/s10/pjm/v3/test/ods_material_info_v2.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
   <si>
     <t>项目编号</t>
   </si>
@@ -484,136 +484,121 @@
     <t>已安排驻厂监造</t>
   </si>
   <si>
+    <t>PJ-2025-007</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
     <t>PJ-2025-008</t>
   </si>
   <si>
-    <t>20250/04/05</t>
-  </si>
-  <si>
     <t>PJ-2025-003</t>
   </si>
   <si>
+    <t>2025.2.25</t>
+  </si>
+  <si>
     <t>PJ-2025-004</t>
   </si>
   <si>
+    <t>2025年3月3日</t>
+  </si>
+  <si>
+    <t>2025-05</t>
+  </si>
+  <si>
+    <t>PJ-2025-005</t>
+  </si>
+  <si>
+    <t>2025-3-16</t>
+  </si>
+  <si>
+    <t>2025/03/25</t>
+  </si>
+  <si>
+    <t>2025-04-32</t>
+  </si>
+  <si>
+    <t>2025-04</t>
+  </si>
+  <si>
+    <t>2025-2-25</t>
+  </si>
+  <si>
+    <t>2025-13-28</t>
+  </si>
+  <si>
+    <t>PJ-2025-006</t>
+  </si>
+  <si>
+    <t>2025年04月10日</t>
+  </si>
+  <si>
+    <t>2025/4/5</t>
+  </si>
+  <si>
+    <t>2025-03-32</t>
+  </si>
+  <si>
+    <t>2025/3/30</t>
+  </si>
+  <si>
+    <t>2025-4-10</t>
+  </si>
+  <si>
+    <t>2025-03</t>
+  </si>
+  <si>
+    <t>2025年3月30日</t>
+  </si>
+  <si>
+    <t>20250/04/03</t>
+  </si>
+  <si>
+    <t>2025-02-30</t>
+  </si>
+  <si>
+    <t>2025-13-15</t>
+  </si>
+  <si>
+    <t>2025年5月1日</t>
+  </si>
+  <si>
+    <t>20205/04/28</t>
+  </si>
+  <si>
+    <t>2025-3-25</t>
+  </si>
+  <si>
+    <t>20250/04/01</t>
+  </si>
+  <si>
+    <t>2025年03月03日</t>
+  </si>
+  <si>
+    <t>2025/04/10</t>
+  </si>
+  <si>
+    <t>2025年2月28日</t>
+  </si>
+  <si>
+    <t>未知</t>
+  </si>
+  <si>
+    <t>2025/03/10</t>
+  </si>
+  <si>
+    <t>20205/03/14</t>
+  </si>
+  <si>
+    <t>2025年6月30日</t>
+  </si>
+  <si>
+    <t>2025-3-12</t>
+  </si>
+  <si>
     <t>待定</t>
-  </si>
-  <si>
-    <t>2025-7-15</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>PJ-2025-005</t>
-  </si>
-  <si>
-    <t>2025/1/25</t>
-  </si>
-  <si>
-    <t>PJ-2025-007</t>
-  </si>
-  <si>
-    <t>2025-02-30</t>
-  </si>
-  <si>
-    <t>PJ-2025-006</t>
-  </si>
-  <si>
-    <t>2025年4月10日</t>
-  </si>
-  <si>
-    <t>20250/02/25</t>
-  </si>
-  <si>
-    <t>2025/04/05</t>
-  </si>
-  <si>
-    <t>20205/02/28</t>
-  </si>
-  <si>
-    <t>2025-13-10</t>
-  </si>
-  <si>
-    <t>20205/03/15</t>
-  </si>
-  <si>
-    <t>2025/3/12</t>
-  </si>
-  <si>
-    <t>未知</t>
-  </si>
-  <si>
-    <t>2025-13-30</t>
-  </si>
-  <si>
-    <t>2025/4/28</t>
-  </si>
-  <si>
-    <t>2025-03</t>
-  </si>
-  <si>
-    <t>2025-01</t>
-  </si>
-  <si>
-    <t>2025-01-32</t>
-  </si>
-  <si>
-    <t>2025年3月12日</t>
-  </si>
-  <si>
-    <t>20250/04/01</t>
-  </si>
-  <si>
-    <t>2025-05</t>
-  </si>
-  <si>
-    <t>2025.4.3</t>
-  </si>
-  <si>
-    <t>20250/02/15</t>
-  </si>
-  <si>
-    <t>2025/4/15</t>
-  </si>
-  <si>
-    <t>2025-4-10</t>
-  </si>
-  <si>
-    <t>2025-2-15</t>
-  </si>
-  <si>
-    <t>20250/03/20</t>
-  </si>
-  <si>
-    <t>20250/03/18</t>
-  </si>
-  <si>
-    <t>2025年4月5日</t>
-  </si>
-  <si>
-    <t>2025/02/25</t>
-  </si>
-  <si>
-    <t>2025-13-15</t>
-  </si>
-  <si>
-    <t>2025.4.28</t>
-  </si>
-  <si>
-    <t>2025/04/10</t>
-  </si>
-  <si>
-    <t>2025/03/12</t>
-  </si>
-  <si>
-    <t>2025/03/18</t>
-  </si>
-  <si>
-    <t>2025-3-1</t>
-  </si>
-  <si>
-    <t>2025.2.10</t>
   </si>
 </sst>
 </file>
@@ -1623,7 +1608,7 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>36</v>
+        <v>159</v>
       </c>
       <c r="I12" t="s">
         <v>37</v>
@@ -1680,7 +1665,7 @@
         <v>51</v>
       </c>
       <c r="AA12" t="s">
-        <v>159</v>
+        <v>52</v>
       </c>
       <c r="AB12" t="s">
         <v>45</v>
@@ -1780,7 +1765,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s">
         <v>72</v>
@@ -1813,7 +1798,7 @@
         <v>77</v>
       </c>
       <c r="L14" t="s">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s">
         <v>79</v>
@@ -1869,7 +1854,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B15" t="s">
         <v>87</v>
@@ -1902,7 +1887,7 @@
         <v>93</v>
       </c>
       <c r="L15" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="M15" t="s">
         <v>93</v>
@@ -1979,13 +1964,13 @@
         <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="I16" t="s">
         <v>77</v>
       </c>
       <c r="J16" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="K16" t="s">
         <v>105</v>
@@ -2047,7 +2032,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
@@ -2080,7 +2065,7 @@
         <v>77</v>
       </c>
       <c r="L17" t="s">
-        <v>164</v>
+        <v>76</v>
       </c>
       <c r="M17" t="s">
         <v>77</v>
@@ -2092,7 +2077,7 @@
         <v>82</v>
       </c>
       <c r="P17" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="Q17" t="s">
         <v>82</v>
@@ -2136,7 +2121,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
         <v>54</v>
@@ -2163,7 +2148,7 @@
         <v>119</v>
       </c>
       <c r="J18" t="s">
-        <v>162</v>
+        <v>120</v>
       </c>
       <c r="K18" t="s">
         <v>121</v>
@@ -2214,7 +2199,7 @@
         <v>51</v>
       </c>
       <c r="AA18" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="AB18" t="s">
         <v>121</v>
@@ -2225,7 +2210,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B19" t="s">
         <v>30</v>
@@ -2270,7 +2255,7 @@
         <v>42</v>
       </c>
       <c r="P19" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="Q19" t="s">
         <v>39</v>
@@ -2303,7 +2288,7 @@
         <v>51</v>
       </c>
       <c r="AA19" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AB19" t="s">
         <v>93</v>
@@ -2314,7 +2299,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B20" t="s">
         <v>87</v>
@@ -2335,7 +2320,7 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="I20" t="s">
         <v>143</v>
@@ -2347,13 +2332,13 @@
         <v>45</v>
       </c>
       <c r="L20" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="M20" t="s">
         <v>70</v>
       </c>
       <c r="N20" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="O20" t="s">
         <v>61</v>
@@ -2403,7 +2388,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>167</v>
+        <v>99</v>
       </c>
       <c r="B21" t="s">
         <v>100</v>
@@ -2424,7 +2409,7 @@
         <v>35</v>
       </c>
       <c r="H21" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="I21" t="s">
         <v>79</v>
@@ -2492,7 +2477,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B22" t="s">
         <v>30</v>
@@ -2519,7 +2504,7 @@
         <v>37</v>
       </c>
       <c r="J22" t="s">
-        <v>168</v>
+        <v>38</v>
       </c>
       <c r="K22" t="s">
         <v>39</v>
@@ -2581,7 +2566,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>169</v>
+        <v>29</v>
       </c>
       <c r="B23" t="s">
         <v>54</v>
@@ -2659,7 +2644,7 @@
         <v>68</v>
       </c>
       <c r="AA23" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="AB23" t="s">
         <v>70</v>
@@ -2670,7 +2655,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B24" t="s">
         <v>72</v>
@@ -2709,7 +2694,7 @@
         <v>79</v>
       </c>
       <c r="N24" t="s">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="O24" t="s">
         <v>77</v>
@@ -2721,7 +2706,7 @@
         <v>77</v>
       </c>
       <c r="R24" t="s">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="S24" t="s">
         <v>82</v>
@@ -2748,7 +2733,7 @@
         <v>51</v>
       </c>
       <c r="AA24" t="s">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="AB24" t="s">
         <v>82</v>
@@ -2759,7 +2744,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>161</v>
       </c>
       <c r="B25" t="s">
         <v>87</v>
@@ -2798,7 +2783,7 @@
         <v>93</v>
       </c>
       <c r="N25" t="s">
-        <v>172</v>
+        <v>52</v>
       </c>
       <c r="O25" t="s">
         <v>45</v>
@@ -2848,7 +2833,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B26" t="s">
         <v>100</v>
@@ -2937,7 +2922,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s">
         <v>30</v>
@@ -2970,7 +2955,7 @@
         <v>77</v>
       </c>
       <c r="L27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M27" t="s">
         <v>77</v>
@@ -2982,7 +2967,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>164</v>
+        <v>113</v>
       </c>
       <c r="Q27" t="s">
         <v>82</v>
@@ -3026,7 +3011,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B28" t="s">
         <v>54</v>
@@ -3047,7 +3032,7 @@
         <v>35</v>
       </c>
       <c r="H28" t="s">
-        <v>174</v>
+        <v>118</v>
       </c>
       <c r="I28" t="s">
         <v>119</v>
@@ -3115,7 +3100,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>165</v>
+        <v>99</v>
       </c>
       <c r="B29" t="s">
         <v>30</v>
@@ -3142,7 +3127,7 @@
         <v>134</v>
       </c>
       <c r="J29" t="s">
-        <v>175</v>
+        <v>38</v>
       </c>
       <c r="K29" t="s">
         <v>39</v>
@@ -3204,7 +3189,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s">
         <v>87</v>
@@ -3293,7 +3278,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B31" t="s">
         <v>100</v>
@@ -3371,7 +3356,7 @@
         <v>156</v>
       </c>
       <c r="AA31" t="s">
-        <v>69</v>
+        <v>174</v>
       </c>
       <c r="AB31" t="s">
         <v>70</v>
@@ -3382,7 +3367,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B32" t="s">
         <v>30</v>
@@ -3415,7 +3400,7 @@
         <v>39</v>
       </c>
       <c r="L32" t="s">
-        <v>176</v>
+        <v>40</v>
       </c>
       <c r="M32" t="s">
         <v>39</v>
@@ -3460,7 +3445,7 @@
         <v>51</v>
       </c>
       <c r="AA32" t="s">
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="AB32" t="s">
         <v>45</v>
@@ -3471,7 +3456,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B33" t="s">
         <v>54</v>
@@ -3498,7 +3483,7 @@
         <v>59</v>
       </c>
       <c r="J33" t="s">
-        <v>177</v>
+        <v>60</v>
       </c>
       <c r="K33" t="s">
         <v>61</v>
@@ -3560,7 +3545,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>161</v>
+        <v>29</v>
       </c>
       <c r="B34" t="s">
         <v>72</v>
@@ -3638,7 +3623,7 @@
         <v>51</v>
       </c>
       <c r="AA34" t="s">
-        <v>86</v>
+        <v>176</v>
       </c>
       <c r="AB34" t="s">
         <v>82</v>
@@ -3649,7 +3634,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B35" t="s">
         <v>87</v>
@@ -3682,13 +3667,13 @@
         <v>93</v>
       </c>
       <c r="L35" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M35" t="s">
         <v>93</v>
       </c>
       <c r="N35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O35" t="s">
         <v>45</v>
@@ -3738,7 +3723,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B36" t="s">
         <v>100</v>
@@ -3816,7 +3801,7 @@
         <v>109</v>
       </c>
       <c r="AA36" t="s">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="AB36" t="s">
         <v>70</v>
@@ -3827,7 +3812,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>173</v>
       </c>
       <c r="B37" t="s">
         <v>30</v>
@@ -3916,7 +3901,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="B38" t="s">
         <v>54</v>
@@ -3949,7 +3934,7 @@
         <v>121</v>
       </c>
       <c r="L38" t="s">
-        <v>179</v>
+        <v>122</v>
       </c>
       <c r="M38" t="s">
         <v>123</v>
@@ -4005,7 +3990,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="B39" t="s">
         <v>30</v>
@@ -4026,13 +4011,13 @@
         <v>49</v>
       </c>
       <c r="H39" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="I39" t="s">
         <v>134</v>
       </c>
       <c r="J39" t="s">
-        <v>180</v>
+        <v>38</v>
       </c>
       <c r="K39" t="s">
         <v>39</v>
@@ -4094,7 +4079,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="B40" t="s">
         <v>87</v>
@@ -4115,7 +4100,7 @@
         <v>35</v>
       </c>
       <c r="H40" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="I40" t="s">
         <v>143</v>
@@ -4183,7 +4168,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B41" t="s">
         <v>100</v>
@@ -4272,7 +4257,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B42" t="s">
         <v>30</v>
@@ -4293,7 +4278,7 @@
         <v>35</v>
       </c>
       <c r="H42" t="s">
-        <v>182</v>
+        <v>36</v>
       </c>
       <c r="I42" t="s">
         <v>37</v>
@@ -4305,7 +4290,7 @@
         <v>39</v>
       </c>
       <c r="L42" t="s">
-        <v>183</v>
+        <v>40</v>
       </c>
       <c r="M42" t="s">
         <v>39</v>
@@ -4323,7 +4308,7 @@
         <v>42</v>
       </c>
       <c r="R42" t="s">
-        <v>184</v>
+        <v>44</v>
       </c>
       <c r="S42" t="s">
         <v>45</v>
@@ -4350,7 +4335,7 @@
         <v>51</v>
       </c>
       <c r="AA42" t="s">
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="AB42" t="s">
         <v>45</v>
@@ -4361,7 +4346,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B43" t="s">
         <v>54</v>
@@ -4400,7 +4385,7 @@
         <v>51</v>
       </c>
       <c r="N43" t="s">
-        <v>185</v>
+        <v>62</v>
       </c>
       <c r="O43" t="s">
         <v>63</v>
@@ -4439,7 +4424,7 @@
         <v>68</v>
       </c>
       <c r="AA43" t="s">
-        <v>174</v>
+        <v>69</v>
       </c>
       <c r="AB43" t="s">
         <v>70</v>
@@ -4450,7 +4435,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>161</v>
+        <v>29</v>
       </c>
       <c r="B44" t="s">
         <v>72</v>
@@ -4501,7 +4486,7 @@
         <v>77</v>
       </c>
       <c r="R44" t="s">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="S44" t="s">
         <v>82</v>
@@ -4539,7 +4524,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B45" t="s">
         <v>87</v>
@@ -4572,7 +4557,7 @@
         <v>93</v>
       </c>
       <c r="L45" t="s">
-        <v>94</v>
+        <v>180</v>
       </c>
       <c r="M45" t="s">
         <v>93</v>
@@ -4584,7 +4569,7 @@
         <v>45</v>
       </c>
       <c r="P45" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q45" t="s">
         <v>45</v>
@@ -4617,7 +4602,7 @@
         <v>51</v>
       </c>
       <c r="AA45" t="s">
-        <v>69</v>
+        <v>182</v>
       </c>
       <c r="AB45" t="s">
         <v>70</v>
@@ -4628,7 +4613,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
       <c r="B46" t="s">
         <v>100</v>
@@ -4655,7 +4640,7 @@
         <v>77</v>
       </c>
       <c r="J46" t="s">
-        <v>104</v>
+        <v>183</v>
       </c>
       <c r="K46" t="s">
         <v>105</v>
@@ -4717,7 +4702,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B47" t="s">
         <v>30</v>
@@ -4806,7 +4791,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>165</v>
+        <v>29</v>
       </c>
       <c r="B48" t="s">
         <v>54</v>
@@ -4833,13 +4818,13 @@
         <v>119</v>
       </c>
       <c r="J48" t="s">
-        <v>120</v>
+        <v>184</v>
       </c>
       <c r="K48" t="s">
         <v>121</v>
       </c>
       <c r="L48" t="s">
-        <v>51</v>
+        <v>185</v>
       </c>
       <c r="M48" t="s">
         <v>123</v>
@@ -4895,7 +4880,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="B49" t="s">
         <v>30</v>
@@ -4916,7 +4901,7 @@
         <v>49</v>
       </c>
       <c r="H49" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
       <c r="I49" t="s">
         <v>134</v>
@@ -4934,13 +4919,13 @@
         <v>39</v>
       </c>
       <c r="N49" t="s">
-        <v>164</v>
+        <v>43</v>
       </c>
       <c r="O49" t="s">
         <v>42</v>
       </c>
       <c r="P49" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="Q49" t="s">
         <v>39</v>
@@ -4973,7 +4958,7 @@
         <v>51</v>
       </c>
       <c r="AA49" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="AB49" t="s">
         <v>93</v>
@@ -4984,7 +4969,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>158</v>
+        <v>29</v>
       </c>
       <c r="B50" t="s">
         <v>87</v>
@@ -5023,7 +5008,7 @@
         <v>70</v>
       </c>
       <c r="N50" t="s">
-        <v>60</v>
+        <v>169</v>
       </c>
       <c r="O50" t="s">
         <v>61</v>
@@ -5062,7 +5047,7 @@
         <v>51</v>
       </c>
       <c r="AA50" t="s">
-        <v>188</v>
+        <v>60</v>
       </c>
       <c r="AB50" t="s">
         <v>61</v>
@@ -5073,7 +5058,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="B51" t="s">
         <v>100</v>
@@ -5162,7 +5147,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B52" t="s">
         <v>30</v>
@@ -5213,7 +5198,7 @@
         <v>42</v>
       </c>
       <c r="R52" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="S52" t="s">
         <v>45</v>
@@ -5251,7 +5236,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B53" t="s">
         <v>54</v>
@@ -5340,7 +5325,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B54" t="s">
         <v>72</v>
@@ -5367,13 +5352,13 @@
         <v>51</v>
       </c>
       <c r="J54" t="s">
-        <v>76</v>
+        <v>172</v>
       </c>
       <c r="K54" t="s">
         <v>77</v>
       </c>
       <c r="L54" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="M54" t="s">
         <v>79</v>
@@ -5385,7 +5370,7 @@
         <v>77</v>
       </c>
       <c r="P54" t="s">
-        <v>76</v>
+        <v>172</v>
       </c>
       <c r="Q54" t="s">
         <v>77</v>
@@ -5429,7 +5414,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="B55" t="s">
         <v>87</v>
@@ -5462,13 +5447,13 @@
         <v>93</v>
       </c>
       <c r="L55" t="s">
-        <v>162</v>
+        <v>94</v>
       </c>
       <c r="M55" t="s">
         <v>93</v>
       </c>
       <c r="N55" t="s">
-        <v>159</v>
+        <v>52</v>
       </c>
       <c r="O55" t="s">
         <v>45</v>
@@ -5539,7 +5524,7 @@
         <v>35</v>
       </c>
       <c r="H56" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="I56" t="s">
         <v>77</v>
@@ -5596,7 +5581,7 @@
         <v>109</v>
       </c>
       <c r="AA56" t="s">
-        <v>189</v>
+        <v>69</v>
       </c>
       <c r="AB56" t="s">
         <v>70</v>
@@ -5607,7 +5592,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B57" t="s">
         <v>30</v>
@@ -5652,13 +5637,13 @@
         <v>82</v>
       </c>
       <c r="P57" t="s">
-        <v>113</v>
+        <v>188</v>
       </c>
       <c r="Q57" t="s">
         <v>82</v>
       </c>
       <c r="R57" t="s">
-        <v>180</v>
+        <v>86</v>
       </c>
       <c r="S57" t="s">
         <v>82</v>
@@ -5696,7 +5681,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>169</v>
+        <v>29</v>
       </c>
       <c r="B58" t="s">
         <v>54</v>
@@ -5785,7 +5770,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B59" t="s">
         <v>30</v>
@@ -5806,7 +5791,7 @@
         <v>49</v>
       </c>
       <c r="H59" t="s">
-        <v>190</v>
+        <v>133</v>
       </c>
       <c r="I59" t="s">
         <v>134</v>
@@ -5830,13 +5815,13 @@
         <v>42</v>
       </c>
       <c r="P59" t="s">
-        <v>180</v>
+        <v>136</v>
       </c>
       <c r="Q59" t="s">
         <v>39</v>
       </c>
       <c r="R59" t="s">
-        <v>191</v>
+        <v>41</v>
       </c>
       <c r="S59" t="s">
         <v>42</v>
@@ -5874,7 +5859,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="B60" t="s">
         <v>87</v>
@@ -5901,7 +5886,7 @@
         <v>143</v>
       </c>
       <c r="J60" t="s">
-        <v>162</v>
+        <v>44</v>
       </c>
       <c r="K60" t="s">
         <v>45</v>
@@ -5919,7 +5904,7 @@
         <v>61</v>
       </c>
       <c r="P60" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="Q60" t="s">
         <v>61</v>
@@ -5963,7 +5948,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B61" t="s">
         <v>100</v>
@@ -6052,7 +6037,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B62" t="s">
         <v>30</v>
@@ -6097,7 +6082,7 @@
         <v>42</v>
       </c>
       <c r="P62" t="s">
-        <v>192</v>
+        <v>43</v>
       </c>
       <c r="Q62" t="s">
         <v>42</v>
@@ -6130,7 +6115,7 @@
         <v>51</v>
       </c>
       <c r="AA62" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="AB62" t="s">
         <v>45</v>
@@ -6141,7 +6126,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="B63" t="s">
         <v>54</v>
@@ -6219,7 +6204,7 @@
         <v>68</v>
       </c>
       <c r="AA63" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="AB63" t="s">
         <v>70</v>
@@ -6230,7 +6215,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B64" t="s">
         <v>72</v>
@@ -6257,19 +6242,19 @@
         <v>51</v>
       </c>
       <c r="J64" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="K64" t="s">
         <v>77</v>
       </c>
       <c r="L64" t="s">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="M64" t="s">
         <v>79</v>
       </c>
       <c r="N64" t="s">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="O64" t="s">
         <v>77</v>
@@ -6319,7 +6304,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B65" t="s">
         <v>87</v>
@@ -6408,7 +6393,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B66" t="s">
         <v>100</v>
@@ -6486,7 +6471,7 @@
         <v>109</v>
       </c>
       <c r="AA66" t="s">
-        <v>69</v>
+        <v>191</v>
       </c>
       <c r="AB66" t="s">
         <v>70</v>
@@ -6497,7 +6482,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B67" t="s">
         <v>30</v>
@@ -6548,7 +6533,7 @@
         <v>82</v>
       </c>
       <c r="R67" t="s">
-        <v>86</v>
+        <v>192</v>
       </c>
       <c r="S67" t="s">
         <v>82</v>
@@ -6575,7 +6560,7 @@
         <v>51</v>
       </c>
       <c r="AA67" t="s">
-        <v>195</v>
+        <v>38</v>
       </c>
       <c r="AB67" t="s">
         <v>39</v>
@@ -6586,7 +6571,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B68" t="s">
         <v>54</v>
@@ -6619,7 +6604,7 @@
         <v>121</v>
       </c>
       <c r="L68" t="s">
-        <v>196</v>
+        <v>122</v>
       </c>
       <c r="M68" t="s">
         <v>123</v>
@@ -6664,7 +6649,7 @@
         <v>51</v>
       </c>
       <c r="AA68" t="s">
-        <v>128</v>
+        <v>191</v>
       </c>
       <c r="AB68" t="s">
         <v>121</v>
@@ -6708,7 +6693,7 @@
         <v>39</v>
       </c>
       <c r="L69" t="s">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="M69" t="s">
         <v>39</v>
@@ -6764,7 +6749,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B70" t="s">
         <v>87</v>
@@ -6797,7 +6782,7 @@
         <v>45</v>
       </c>
       <c r="L70" t="s">
-        <v>189</v>
+        <v>69</v>
       </c>
       <c r="M70" t="s">
         <v>70</v>
@@ -6842,7 +6827,7 @@
         <v>51</v>
       </c>
       <c r="AA70" t="s">
-        <v>60</v>
+        <v>183</v>
       </c>
       <c r="AB70" t="s">
         <v>61</v>
@@ -6853,7 +6838,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>167</v>
+        <v>99</v>
       </c>
       <c r="B71" t="s">
         <v>100</v>
@@ -6880,7 +6865,7 @@
         <v>79</v>
       </c>
       <c r="J71" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="K71" t="s">
         <v>153</v>
@@ -6931,7 +6916,7 @@
         <v>156</v>
       </c>
       <c r="AA71" t="s">
-        <v>197</v>
+        <v>69</v>
       </c>
       <c r="AB71" t="s">
         <v>70</v>
@@ -6942,7 +6927,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B72" t="s">
         <v>30</v>
@@ -6969,13 +6954,13 @@
         <v>37</v>
       </c>
       <c r="J72" t="s">
-        <v>195</v>
+        <v>38</v>
       </c>
       <c r="K72" t="s">
         <v>39</v>
       </c>
       <c r="L72" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="M72" t="s">
         <v>39</v>
@@ -6987,7 +6972,7 @@
         <v>42</v>
       </c>
       <c r="P72" t="s">
-        <v>199</v>
+        <v>43</v>
       </c>
       <c r="Q72" t="s">
         <v>42</v>
@@ -7031,7 +7016,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B73" t="s">
         <v>54</v>
@@ -7070,7 +7055,7 @@
         <v>51</v>
       </c>
       <c r="N73" t="s">
-        <v>185</v>
+        <v>62</v>
       </c>
       <c r="O73" t="s">
         <v>63</v>
@@ -7120,7 +7105,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B74" t="s">
         <v>72</v>
@@ -7209,7 +7194,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="B75" t="s">
         <v>87</v>
@@ -7287,7 +7272,7 @@
         <v>51</v>
       </c>
       <c r="AA75" t="s">
-        <v>69</v>
+        <v>196</v>
       </c>
       <c r="AB75" t="s">
         <v>70</v>
@@ -7319,7 +7304,7 @@
         <v>35</v>
       </c>
       <c r="H76" t="s">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="I76" t="s">
         <v>77</v>
@@ -7376,7 +7361,7 @@
         <v>109</v>
       </c>
       <c r="AA76" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="AB76" t="s">
         <v>70</v>
@@ -7387,7 +7372,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B77" t="s">
         <v>30</v>
@@ -7414,7 +7399,7 @@
         <v>51</v>
       </c>
       <c r="J77" t="s">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="K77" t="s">
         <v>77</v>
@@ -7476,7 +7461,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>29</v>
+        <v>160</v>
       </c>
       <c r="B78" t="s">
         <v>54</v>
@@ -7497,7 +7482,7 @@
         <v>35</v>
       </c>
       <c r="H78" t="s">
-        <v>201</v>
+        <v>118</v>
       </c>
       <c r="I78" t="s">
         <v>119</v>
@@ -7515,7 +7500,7 @@
         <v>123</v>
       </c>
       <c r="N78" t="s">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="O78" t="s">
         <v>63</v>
@@ -7565,7 +7550,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>165</v>
+        <v>29</v>
       </c>
       <c r="B79" t="s">
         <v>30</v>
@@ -7598,7 +7583,7 @@
         <v>39</v>
       </c>
       <c r="L79" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="M79" t="s">
         <v>39</v>
@@ -7610,13 +7595,13 @@
         <v>42</v>
       </c>
       <c r="P79" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="Q79" t="s">
         <v>39</v>
       </c>
       <c r="R79" t="s">
-        <v>51</v>
+        <v>196</v>
       </c>
       <c r="S79" t="s">
         <v>42</v>
@@ -7654,7 +7639,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="B80" t="s">
         <v>87</v>
@@ -7699,7 +7684,7 @@
         <v>61</v>
       </c>
       <c r="P80" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="Q80" t="s">
         <v>61</v>
@@ -7732,7 +7717,7 @@
         <v>51</v>
       </c>
       <c r="AA80" t="s">
-        <v>188</v>
+        <v>60</v>
       </c>
       <c r="AB80" t="s">
         <v>61</v>
@@ -7743,7 +7728,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B81" t="s">
         <v>100</v>
